--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-CYC-4/08-report/CYC-4-cycle-report.xlsx
@@ -168,7 +168,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 10 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 79 passed and 4 failed (pass rate 95.2%). 4 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-007 A 15-night stay in Paris is rejected: returns 200 instead of 400; DEF-008 Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409.</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/Agentic-QE-MVP@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 10 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 79 passed and 4 failed (pass rate 95.2%). 4 defect(s) were raised from real failures: DEF-001 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-002 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-007 A 15-night stay in Paris is rejected: returns 200 instead of 400; DEF-008 Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -201,19 +201,19 @@
     <t>jira-export</t>
   </si>
   <si>
-    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export, release-2.0 snapshot): Jira REST API v3 JSON of AQPI-32, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+    <t>Jira export on GitHub (sri465inno/Agentic-QE-MVP@demo/jira-export, release-2.0 snapshot): Jira REST API v3 JSON of AQPI-32, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
   </si>
   <si>
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44)</t>
+    <t>sri465inno/Agentic-QE-MVP@demo/hotel-booking-platform-v2 (fe1ce44)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:27:15.652Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/Agentic-QE-MVP@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-05T16:44:02.549Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5566,7 +5566,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:17.630Z</t>
+    <t>2026-10-05T16:44:05.345Z</t>
   </si>
   <si>
     <t>33 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5578,7 +5578,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-05T16:27:17.672Z</t>
+    <t>2026-10-05T16:44:05.386Z</t>
   </si>
   <si>
     <t>13 requirements, 18 test cases, 10 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -26217,7 +26217,7 @@
         <v>1430</v>
       </c>
       <c r="E2" s="2">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -26335,7 +26335,7 @@
         <v>1430</v>
       </c>
       <c r="E8" s="2">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -26353,7 +26353,7 @@
         <v>1430</v>
       </c>
       <c r="E9" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -26371,7 +26371,7 @@
         <v>1430</v>
       </c>
       <c r="E10" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -26389,7 +26389,7 @@
         <v>1430</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -26425,7 +26425,7 @@
         <v>1430</v>
       </c>
       <c r="E13" s="2">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -26521,7 +26521,7 @@
         <v>1430</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -26579,7 +26579,7 @@
         <v>1430</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F21" s="2"/>
     </row>
@@ -26617,7 +26617,7 @@
         <v>1430</v>
       </c>
       <c r="E23" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -26635,7 +26635,7 @@
         <v>1430</v>
       </c>
       <c r="E24" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F24" s="2"/>
     </row>
@@ -26653,7 +26653,7 @@
         <v>1430</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2"/>
     </row>
@@ -26671,7 +26671,7 @@
         <v>1430</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F26" s="2"/>
     </row>
@@ -26689,7 +26689,7 @@
         <v>1430</v>
       </c>
       <c r="E27" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F27" s="2"/>
     </row>
@@ -26707,7 +26707,7 @@
         <v>1430</v>
       </c>
       <c r="E28" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F28" s="2"/>
     </row>
@@ -26725,7 +26725,7 @@
         <v>1430</v>
       </c>
       <c r="E29" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F29" s="2"/>
     </row>
@@ -26743,7 +26743,7 @@
         <v>1430</v>
       </c>
       <c r="E30" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" s="2"/>
     </row>
@@ -26761,7 +26761,7 @@
         <v>1430</v>
       </c>
       <c r="E31" s="2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F31" s="2"/>
     </row>
@@ -26799,7 +26799,7 @@
         <v>1430</v>
       </c>
       <c r="E33" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F33" s="2"/>
     </row>
@@ -26817,7 +26817,7 @@
         <v>1430</v>
       </c>
       <c r="E34" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F34" s="2"/>
     </row>
@@ -26875,7 +26875,7 @@
         <v>1430</v>
       </c>
       <c r="E37" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2"/>
     </row>
@@ -26913,7 +26913,7 @@
         <v>1430</v>
       </c>
       <c r="E39" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F39" s="2"/>
     </row>
@@ -26931,7 +26931,7 @@
         <v>1430</v>
       </c>
       <c r="E40" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
     </row>
@@ -27029,7 +27029,7 @@
         <v>1430</v>
       </c>
       <c r="E45" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F45" s="2"/>
     </row>
@@ -27047,7 +27047,7 @@
         <v>1430</v>
       </c>
       <c r="E46" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F46" s="2"/>
     </row>
@@ -27065,7 +27065,7 @@
         <v>1430</v>
       </c>
       <c r="E47" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2"/>
     </row>
@@ -27103,7 +27103,7 @@
         <v>1430</v>
       </c>
       <c r="E49" s="2">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="F49" s="2"/>
     </row>
@@ -27121,7 +27121,7 @@
         <v>1430</v>
       </c>
       <c r="E50" s="2">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F50" s="2"/>
     </row>
@@ -27139,7 +27139,7 @@
         <v>1430</v>
       </c>
       <c r="E51" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F51" s="2"/>
     </row>
@@ -27257,7 +27257,7 @@
         <v>1430</v>
       </c>
       <c r="E57" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F57" s="2"/>
     </row>
@@ -27275,7 +27275,7 @@
         <v>1430</v>
       </c>
       <c r="E58" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F58" s="2"/>
     </row>
@@ -27313,7 +27313,7 @@
         <v>1430</v>
       </c>
       <c r="E60" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F60" s="2"/>
     </row>
@@ -27411,7 +27411,7 @@
         <v>1430</v>
       </c>
       <c r="E65" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F65" s="2"/>
     </row>
@@ -27429,7 +27429,7 @@
         <v>1430</v>
       </c>
       <c r="E66" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
     </row>
@@ -27505,7 +27505,7 @@
         <v>1430</v>
       </c>
       <c r="E70" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F70" s="2"/>
     </row>
@@ -27523,7 +27523,7 @@
         <v>1430</v>
       </c>
       <c r="E71" s="2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2"/>
     </row>
@@ -27541,7 +27541,7 @@
         <v>1430</v>
       </c>
       <c r="E72" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2"/>
     </row>
@@ -27579,7 +27579,7 @@
         <v>1430</v>
       </c>
       <c r="E74" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F74" s="2"/>
     </row>
@@ -27597,7 +27597,7 @@
         <v>1430</v>
       </c>
       <c r="E75" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F75" s="2"/>
     </row>
@@ -27615,7 +27615,7 @@
         <v>1430</v>
       </c>
       <c r="E76" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F76" s="2"/>
     </row>
@@ -27633,7 +27633,7 @@
         <v>1430</v>
       </c>
       <c r="E77" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F77" s="2"/>
     </row>
@@ -27691,7 +27691,7 @@
         <v>1430</v>
       </c>
       <c r="E80" s="2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F80" s="2"/>
     </row>
@@ -27709,7 +27709,7 @@
         <v>1430</v>
       </c>
       <c r="E81" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F81" s="2"/>
     </row>
@@ -27727,7 +27727,7 @@
         <v>1430</v>
       </c>
       <c r="E82" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F82" s="2"/>
     </row>
@@ -27805,7 +27805,7 @@
         <v>1430</v>
       </c>
       <c r="E86" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F86" s="2"/>
     </row>
@@ -27823,7 +27823,7 @@
         <v>1430</v>
       </c>
       <c r="E87" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F87" s="2"/>
     </row>
@@ -27841,7 +27841,7 @@
         <v>1430</v>
       </c>
       <c r="E88" s="2">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F88" s="2"/>
     </row>
@@ -27859,7 +27859,7 @@
         <v>1430</v>
       </c>
       <c r="E89" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F89" s="2"/>
     </row>
@@ -27877,7 +27877,7 @@
         <v>1430</v>
       </c>
       <c r="E90" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F90" s="2"/>
     </row>
@@ -27953,7 +27953,7 @@
         <v>1430</v>
       </c>
       <c r="E94" s="2">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="F94" s="2"/>
     </row>
@@ -28031,7 +28031,7 @@
         <v>1430</v>
       </c>
       <c r="E98" s="2">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F98" s="2"/>
     </row>
@@ -28149,7 +28149,7 @@
         <v>1430</v>
       </c>
       <c r="E104" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F104" s="2"/>
     </row>
@@ -28325,7 +28325,7 @@
         <v>1430</v>
       </c>
       <c r="E113" s="2">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F113" s="2"/>
     </row>
@@ -28421,7 +28421,7 @@
         <v>1430</v>
       </c>
       <c r="E118" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F118" s="2"/>
     </row>
@@ -28439,7 +28439,7 @@
         <v>1433</v>
       </c>
       <c r="E119" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F119" s="2"/>
     </row>
@@ -28457,7 +28457,7 @@
         <v>1430</v>
       </c>
       <c r="E120" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F120" s="2"/>
     </row>
@@ -28493,7 +28493,7 @@
         <v>1433</v>
       </c>
       <c r="E122" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F122" s="2"/>
     </row>
@@ -28511,7 +28511,7 @@
         <v>1430</v>
       </c>
       <c r="E123" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F123" s="2"/>
     </row>
@@ -28529,7 +28529,7 @@
         <v>1430</v>
       </c>
       <c r="E124" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F124" s="2"/>
     </row>
@@ -28547,7 +28547,7 @@
         <v>1430</v>
       </c>
       <c r="E125" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2"/>
     </row>
@@ -28565,7 +28565,7 @@
         <v>1430</v>
       </c>
       <c r="E126" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F126" s="2"/>
     </row>
@@ -28583,7 +28583,7 @@
         <v>1433</v>
       </c>
       <c r="E127" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F127" s="2"/>
     </row>
@@ -28601,7 +28601,7 @@
         <v>1430</v>
       </c>
       <c r="E128" s="2">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F128" s="2"/>
     </row>
@@ -28619,7 +28619,7 @@
         <v>1430</v>
       </c>
       <c r="E129" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F129" s="2"/>
     </row>
@@ -28637,7 +28637,7 @@
         <v>1430</v>
       </c>
       <c r="E130" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F130" s="2"/>
     </row>
@@ -28673,7 +28673,7 @@
         <v>1430</v>
       </c>
       <c r="E132" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F132" s="2"/>
     </row>
@@ -28691,7 +28691,7 @@
         <v>1430</v>
       </c>
       <c r="E133" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F133" s="2"/>
     </row>
@@ -28749,7 +28749,7 @@
         <v>1430</v>
       </c>
       <c r="E136" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F136" s="2"/>
     </row>
@@ -28785,7 +28785,7 @@
         <v>1430</v>
       </c>
       <c r="E138" s="2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F138" s="2"/>
     </row>
@@ -28803,7 +28803,7 @@
         <v>1430</v>
       </c>
       <c r="E139" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F139" s="2"/>
     </row>
@@ -28821,7 +28821,7 @@
         <v>1430</v>
       </c>
       <c r="E140" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F140" s="2"/>
     </row>
@@ -28839,7 +28839,7 @@
         <v>1430</v>
       </c>
       <c r="E141" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F141" s="2"/>
     </row>
@@ -28857,7 +28857,7 @@
         <v>1433</v>
       </c>
       <c r="E142" s="2">
-        <v>383</v>
+        <v>444</v>
       </c>
       <c r="F142" s="2"/>
     </row>
@@ -28875,7 +28875,7 @@
         <v>1430</v>
       </c>
       <c r="E143" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F143" s="2"/>
     </row>
@@ -28893,7 +28893,7 @@
         <v>1430</v>
       </c>
       <c r="E144" s="2">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="F144" s="2"/>
     </row>
